--- a/output/pdf_financials_xlsx/TEST.H.xlsx
+++ b/output/pdf_financials_xlsx/TEST.H.xlsx
@@ -729,31 +729,31 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.343686</v>
+        <v>0.510976</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.543951</v>
+        <v>5.237508</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.668825</v>
+        <v>4.510153</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.899255</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.042798</v>
+        <v>3.288951</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.008285000000000001</v>
+        <v>0.609946</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.144011</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>1.102901</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>0.137816</v>
       </c>
     </row>
     <row r="11">
@@ -773,25 +773,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.543265</v>
+        <v>-4.384593</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.899255</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.042798</v>
+        <v>-3.288951</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.008285000000000001</v>
+        <v>-0.609946</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0</v>
+        <v>-0.144011</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0</v>
+        <v>-1.102901</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>-0.137816</v>
       </c>
     </row>
     <row r="12">
@@ -801,16 +801,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00333</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.109871</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.037132</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022825</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1379,16 +1379,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.507646</v>
+        <v>-0.510976</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.127637</v>
+        <v>-5.237508</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.127637</v>
+        <v>-5.164769</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.674357</v>
+        <v>-2.651532</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-10.637</v>
@@ -1447,16 +1447,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.507646</v>
+        <v>-0.510976</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.127637</v>
+        <v>-5.237508</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.127637</v>
+        <v>-5.164769</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.631501</v>
+        <v>-2.608676</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-10.534661</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-2046.642239332</v>
+        <v>-2061.463085587473</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -1622,31 +1622,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.075773</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.259958</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.718152</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.61692</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.551005</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.31301</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.208446</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.261106</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.128597</v>
       </c>
     </row>
     <row r="35">
@@ -1690,31 +1690,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.075773</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.259958</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.718152</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.61692</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.551005</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.31301</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.208446</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.261106</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.128597</v>
       </c>
     </row>
     <row r="37">
@@ -2098,22 +2098,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.183273</v>
+        <v>0.1075</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.071571</v>
+        <v>1.811613</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.627163</v>
+        <v>0.909011</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.664706</v>
+        <v>0.047786</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.615649</v>
+        <v>0.06464399999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.34405</v>
+        <v>0.03104</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -21816,7 +21816,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E288" s="5" t="n">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E309" s="5" t="n">
@@ -24154,7 +24154,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E315" s="5" t="n">

--- a/output/pdf_financials_xlsx/TEST.H.xlsx
+++ b/output/pdf_financials_xlsx/TEST.H.xlsx
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0</v>
+        <v>0.007349</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.088079</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.175038</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0.042856</v>
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.510976</v>
+        <v>-0.503627</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.237508</v>
+        <v>-5.149429</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.164769</v>
+        <v>-4.989731</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.608676</v>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-2061.463085587473</v>
+        <v>-1991.598513604668</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -3899,13 +3899,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.007349</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.088079</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.175038</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -4319,13 +4319,13 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.022358</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.004513</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.037323</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -11832,7 +11832,11 @@
           <t>Proceeds from sale of property and equipment (Note 5)</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -13662,7 +13666,11 @@
           <t>Depreciation of property and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -14998,7 +15006,11 @@
           <t>Depreciation of property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E163" s="5" t="n">
         <v>0.007349</v>
       </c>
@@ -15724,7 +15736,11 @@
           <t>Depreciation of property and equipment (Note 5) 7,349</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E175" s="5" t="n">
         <v>0.003497</v>
       </c>

--- a/output/pdf_financials_xlsx/TEST.H.xlsx
+++ b/output/pdf_financials_xlsx/TEST.H.xlsx
@@ -1118,16 +1118,16 @@
         <v>-5.127637</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-2.674357</v>
+        <v>-0.884312</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-10.637</v>
+        <v>-10.566508</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-1.122963</v>
+        <v>-1.155413</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-0.098888</v>
+        <v>-0.106688</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-1.087723</v>
@@ -3874,16 +3874,16 @@
         <v>-5.127637</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-2.674357</v>
+        <v>-0.884312</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-10.637</v>
+        <v>-10.566508</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-1.122963</v>
+        <v>-1.155413</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>-0.098888</v>
+        <v>-0.106688</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-1.087723</v>
@@ -10618,7 +10618,11 @@
           <t>Loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -16057,7 +16061,11 @@
           <t>Proceeds from share issuances (Note 8) 1,007,721</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E180" s="5" t="n">
         <v>1.966531</v>
       </c>
@@ -17762,7 +17770,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -18604,7 +18616,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
